--- a/artfynd/A 29141-2021 artfynd.xlsx
+++ b/artfynd/A 29141-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 29141-2021 artfynd.xlsx
+++ b/artfynd/A 29141-2021 artfynd.xlsx
@@ -3815,7 +3815,7 @@
         <v>100350543</v>
       </c>
       <c r="B29" t="n">
-        <v>96251</v>
+        <v>98092</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3852,10 +3852,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>550962.5561077876</v>
+        <v>550962</v>
       </c>
       <c r="R29" t="n">
-        <v>6897728.361384262</v>
+        <v>6897728</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3885,19 +3885,9 @@
           <t>2021-10-11</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2021-10-11</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD29" t="b">

--- a/artfynd/A 29141-2021 artfynd.xlsx
+++ b/artfynd/A 29141-2021 artfynd.xlsx
@@ -3815,7 +3815,7 @@
         <v>100350543</v>
       </c>
       <c r="B29" t="n">
-        <v>98092</v>
+        <v>98102</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>

--- a/artfynd/A 29141-2021 artfynd.xlsx
+++ b/artfynd/A 29141-2021 artfynd.xlsx
@@ -3815,7 +3815,7 @@
         <v>100350543</v>
       </c>
       <c r="B29" t="n">
-        <v>98102</v>
+        <v>98114</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>

--- a/artfynd/A 29141-2021 artfynd.xlsx
+++ b/artfynd/A 29141-2021 artfynd.xlsx
@@ -3815,7 +3815,7 @@
         <v>100350543</v>
       </c>
       <c r="B29" t="n">
-        <v>98114</v>
+        <v>98119</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>

--- a/artfynd/A 29141-2021 artfynd.xlsx
+++ b/artfynd/A 29141-2021 artfynd.xlsx
@@ -3815,7 +3815,7 @@
         <v>100350543</v>
       </c>
       <c r="B29" t="n">
-        <v>98119</v>
+        <v>98128</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3829,11 +3829,6 @@
       </c>
       <c r="E29" t="n">
         <v>219790</v>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Fläcknycklar</t>
-        </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>

--- a/artfynd/A 29141-2021 artfynd.xlsx
+++ b/artfynd/A 29141-2021 artfynd.xlsx
@@ -3815,7 +3815,7 @@
         <v>100350543</v>
       </c>
       <c r="B29" t="n">
-        <v>98128</v>
+        <v>98141</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3829,6 +3829,11 @@
       </c>
       <c r="E29" t="n">
         <v>219790</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>

--- a/artfynd/A 29141-2021 artfynd.xlsx
+++ b/artfynd/A 29141-2021 artfynd.xlsx
@@ -3815,7 +3815,7 @@
         <v>100350543</v>
       </c>
       <c r="B29" t="n">
-        <v>98141</v>
+        <v>98154</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>

--- a/artfynd/A 29141-2021 artfynd.xlsx
+++ b/artfynd/A 29141-2021 artfynd.xlsx
@@ -3815,7 +3815,7 @@
         <v>100350543</v>
       </c>
       <c r="B29" t="n">
-        <v>98154</v>
+        <v>98157</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>

--- a/artfynd/A 29141-2021 artfynd.xlsx
+++ b/artfynd/A 29141-2021 artfynd.xlsx
@@ -3815,7 +3815,7 @@
         <v>100350543</v>
       </c>
       <c r="B29" t="n">
-        <v>98157</v>
+        <v>98158</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>

--- a/artfynd/A 29141-2021 artfynd.xlsx
+++ b/artfynd/A 29141-2021 artfynd.xlsx
@@ -3815,7 +3815,7 @@
         <v>100350543</v>
       </c>
       <c r="B29" t="n">
-        <v>98158</v>
+        <v>98161</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>

--- a/artfynd/A 29141-2021 artfynd.xlsx
+++ b/artfynd/A 29141-2021 artfynd.xlsx
@@ -3815,7 +3815,7 @@
         <v>100350543</v>
       </c>
       <c r="B29" t="n">
-        <v>98161</v>
+        <v>98264</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
